--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0023.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0023.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Ta nhất định sẽ tìm một chỗ đàng hoàng để cất giữ thanh kiếm và khiên này an toàn.</t>
+          <t>Tao nhất định sẽ tìm một chỗ đàng hoàng để cất giữ thanh kiếm và khiên này an toàn.</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Encore?</t>
+          <t>Encore à?</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Muốn đoán xem ta phát hiện ra thế nào không?</t>
+          <t>Muốn đoán xem tao phát hiện ra thế nào không?</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Xem cái này đi, Cosmos. Toàn vàng óng ánh, giống như mắt của Rover vậy!</t>
+          <t>Xem cái này đi, Cosmos. Toàn vàng óng ánh, giống như mắt của Vận Mệnh Giả vậy!</t>
         </is>
       </c>
     </row>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Ta bảo rồi mà, sẽ không trễ đâu.</t>
+          <t>Tao bảo rồi mà, sẽ không trễ đâu.</t>
         </is>
       </c>
     </row>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Ta biết. Thiếu mất nhụy hoa rồi. Ta vẫn luôn muốn mẹ được thấy cả vườn diên vĩ nở rộ...</t>
+          <t>Tao biết. Thiếu mất nhụy hoa rồi. Tao vẫn luôn muốn mẹ được thấy cả vườn diên vĩ nở rộ...</t>
         </is>
       </c>
     </row>
@@ -16109,7 +16109,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Những trận đấu đó vẫn hơi quá thật với ta.</t>
+          <t>Những trận đấu đó vẫn hơi quá thật với tao.</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Chắc chắn rồi.</t>
+          <t>Được thôi.</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Pfft. Ta sẽ chọn danh dự, thế thì mới nổi tiếng chứ, ai nhìn thấy ta cũng phải hô tên lên!</t>
+          <t>Pfft. Tao sẽ chọn danh dự, thế thì mới nổi tiếng chứ, ai nhìn thấy tao cũng phải hô tên lên!</t>
         </is>
       </c>
     </row>
@@ -23909,7 +23909,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Ta muốn cô ấy cũng được thấy nó...</t>
+          <t>Tao muốn cô ấy cũng được thấy nó...</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26444,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Ta muốn tự mình đi dạo xung quanh.</t>
+          <t>Tao muốn tự mình đi dạo xung quanh.</t>
         </is>
       </c>
     </row>
@@ -26704,7 +26704,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Tới nơi rồi, ta phải bắt cô ta khai ra hết chỗ giấu kho báu mới được...</t>
+          <t>Tới nơi rồi, tao phải bắt cô ta khai ra hết chỗ giấu kho báu mới được...</t>
         </is>
       </c>
     </row>
@@ -27224,7 +27224,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Ta gặp một họa sĩ tên Zhezhi trong Lễ Hội Đuổi Trăng. Chúng ta đã chơi vui lắm trong lễ hội.</t>
+          <t>Tao gặp một họa sĩ tên Zhezhi trong Lễ Hội Đuổi Trăng. Chúng tao đã chơi vui lắm trong lễ hội.</t>
         </is>
       </c>
     </row>
@@ -27289,7 +27289,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Lần đầu ta thấy cô ấy, cô ấy đang say sưa vẽ phong cảnh, đến mức khi nói chuyện với ta, tâm trí cô vẫn còn đắm chìm trong đó.</t>
+          <t>Lần đầu tao thấy cô ấy, cô ấy đang say sưa vẽ phong cảnh, đến mức khi nói chuyện với tao, tâm trí cô vẫn còn đắm chìm trong đó.</t>
         </is>
       </c>
     </row>
